--- a/output_excel/17176272.xlsx
+++ b/output_excel/17176272.xlsx
@@ -567,7 +567,7 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>CONDIÇÕES | ODD | (DCIM) | BF-A | 1x2x4AC | ANCORAR | 3x336AN | 112,5KVA | BF-A | 37,5KVA | 37,5KVA | 112,5KVA | 112,5KVA | 37,5KVA | CAMPO | 3x336AN | 112,5KVA | 3x336AN | 37,5KVA | 112,5KVA | 37,5KVA | 112,5KVA | BT | 112,5KVA | 37,5KVA | AVENIDA | 37,5KVA | 112,5KVA | 112,5KVA | CONEX. | IP | P8 | (DCIM) | 112,5KVA112,5KVA | 112,5KVA | AVENIDA | (DCIM) | (DCIM) | (DCIM) | 112,5KVA | 112,5KVA | V1-9 | (DCIM) | (KL) | 30K | 112,5KVA | 112,5KVA | 30K | 30K | BF-A | (KL) | 112,5KVA | 30K | BF-A | 1AF(1) | 30K | CONEX. | 16M | 112,5KVA | 30K | BF-A | 112,5KVA | (DCIM) | 112,5KVA | CONEX. | 112,5KVA | CABOS</t>
+          <t>CONDIÇÕES | ODD | (DCIM) | ANCORAR | BF-A | 4 | 6 | 2 | BF-A | 7 | 7 | 112,5KVA | 2 | 7 | 2 | 6 | CAMPO | 6 | 7 | 112,5KVA | 7 | 1 | BT | 1 | 7 | AVENIDA | 7 | 1 | 1 | CONEX. | IP | (DCIM) | 1112,5KVA | 2 | AVENIDA | (DCIM) | (DCIM) | (DCIM) | 1 | 112,5KVA | 9 | (KL) | (DCIM) | 0 | 112,5KVA | 1 | 3 | 0 | BF-A | (KL) | 1 | 3 | BF-A | 1AF(1) | 0 | CONEX. | 16M | 1 | 0 | 2 | BF-A | (DCIM) | 1 | CONEX.</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
@@ -612,11 +612,11 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>BT | MT | V7-8 | 1x3x120(70)AX | 3x70AX(5AZN) | CABOS | ANCORAR | 3x336AN | 112,5KVA | 33.99M | 33.99M | YOSHIDA | 112,5KVA | P7x | B1F | CABOS | ANCORAR | (DCIM) | 36.88M | AV. | V6-7 | P8 | BT | 1x3x120(70)AX</t>
+          <t>BT | MT | 1x3x120(70)AX | 3x70AX(5AZN) | CABOS | ANCORAR | 3x336AN | 112,5KVA</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>P7x | CABOS | ANCORAR | 3x336AN | 112,5KVA | YOSHIDA | 7M | 10M | LC | 112,5KVA | BF-A | BF-A | B1F | CABOS | ANCORAR | (DCIM) | QX16 | TX10 | AV. | V7-8 | 112,5KVA | 112,5KVA | BT | RAMAL | MT | C12X300112,5KVACE1112,5KVAIP | BT | SMTG112,5KVAL1(2) | 1x3x120(70)AX | 3x70AX(5AZN) | BF-A | 16M | QX16 | 112,5KVA | 30K | 112,5KVA | BF-A | CONEX. | 112,5KVA | Q/R | V6-7 | 30K | (DCIM) | 112,5KVA | P8 | 30K | 112,5KVA | BF-A | 112,5KVA | CONEX. | V1-9 | BT | (DCIM) | 112,5KVA</t>
+          <t>CABOS | ANCORAR | 3x336AN | 112,5KVA | YOSHIDA | 7M | 112,5KVA | 10M | LC | BF-A | B1F | BF-A | CABOS | ANCORAR | (DCIM) | QX16 | TX10 | AV. | BT | MT | 1 | 1 | RAMAL | C12X300112,5KVACE1112,5KVAIP | BT | SMTG112,5KVAL1(2) | 1x3x120(70)AX | 3x70AX(5AZN) | BF-A | 16M | QX16 | 1 | 0 | 1 | BF-A | CONEX. | 1 | 3 | Q/R | (DCIM) | 1 | 0 | BF-A | 1 | 1 | CONEX. | 9 | BT | (DCIM) | 1</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
@@ -706,7 +706,7 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | V6-7 | 3x70AX(5AZN) | MT | BT | 36.88M | AV. | (DCIM) | 36.88M | ANCORAR | CABOS | B1F | 112,5KVA | YOSHIDA | 112,5KVA | 3x336AN | ANCORAR | BM | CABOS | 37.01M | MT | 37.01M | 3x70AX(5AZN) | V5-6 | 1x3x120(70)AX | P7x | BT</t>
+          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | MT | BT | 36.88M | AV. | (DCIM) | 36.88M | ANCORAR | CABOS | B1F | 112,5KVA</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>P6 | BM | 566992 | BT | AV. | V5-6 | (DCIM) | 175ET005296879 | ANCORAR | BT | 13200 | V6-7 | BT | MT | CABOS | 33M | 1x3x120(70)AX | BF-A | 45KVA | BF-A | B1F | RAMAL | MT | 1x3x120(70)AX | 112,5KVA | LC | C10x600,B1M,M3F | 3x70AX(5AZN) | 3x70AX(5AZN) | INSTALAÇÃO | 112,5KVA | QX16 | YOSHIDA | BF-A | 7M | VEGETAL | TX10</t>
+          <t>BM | 566992 | BT | AV. | (DCIM) | 175ET005296879 | ANCORAR | BT | 13200 | BT | MT | CABOS | 33M | 1x3x120(70)AX | BF-A | 45KVA | BF-A | B1F | RAMAL | MT | 1x3x120(70)AX | 112,5KVA | LC | C10x600,B1M,M3F | 3x70AX(5AZN) | 3x70AX(5AZN) | INSTALAÇÃO | 1 | QX16 | YOSHIDA | BF-A | 7M | VEGETAL | TX10</t>
         </is>
       </c>
       <c r="I6" s="4" t="n">
@@ -800,11 +800,11 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>V5-6 | 1x3x120(70)AX | BT | MT | 3x70AX(5AZN) | 37.01M | 37.01M | BM | P6 | MT | BT | 3x70AX(5AZN) | 1x3x120(70)AX | V6-7 | BT | 33M</t>
+          <t>BT | MT | 1x3x120(70)AX | 3x70AX(5AZN)</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -837,27 +837,19 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>P5 | LC | C12X600112,5KVACE4112,5KVAIP | 33M | BF-A | SMPI | TX10 | 112,5KVA | V4-5 | BT | RAMAIS | 1x3x120(70)AX | 30K | SMFL112,5KVAL1(2) | MT | MT | C12X600112,5KVACE2112,5KVAIP | BT | 3x70AX(5AZN) | V5-6 | XX | 3x70AX(5AZN) | 1x3x120(70)AX | 29.14M | P6 | P4-30</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>BT | MT | 1x3x120(70)AX | 3x70AX(5AZN) | 33M</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -886,27 +878,19 @@
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>V4-5 | BT | MT | 1x3x120(70)AX | XX | 3x70AX(5AZN) | P4-30 | LC | P5 | 35.33M | C12X600112,5KVACE2112,5KVAIP | SMFL112,5KVAL1(2) | 35.33M | RAMAIS | 30K | 1x3x120(70)AX | V3-4 | C12X600112,5KVACE4112,5KVAIP | 29.14M | 3x70AX(5AZN) | BT | 29.14M | MT | SMPI</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>BT | MT | 1x3x120(70)AX | XX | 3x70AX(5AZN) | LC</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -936,14 +920,14 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35.33m</t>
+          <t>29.14m</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>XX | 35.33M | 1x3x120(70)AX | P4-30 | V3-4 | 35.33M | 3x70AX(5AZN) | BT | MT | MT | BT | V4-5 | 3x70AX(5AZN) | 1x3x120(70)AX | C12X600112,5KVACE2112,5KVAIP | SMFL112,5KVAL1(2) | LC | RAMAIS | 30K | 37.76M</t>
+          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | MT | 29.14M</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
@@ -980,27 +964,19 @@
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>P31 | 30K | BF-A | 112,5KVA | 112,5KVA | 2x1/0AN(4ANA) | INSTALAÇÃO | 1x3x120(70)AX | BT | B1F | C12X300112,5KVACEAFS112,5KVASMTG112,5KVAL1(2)112,5KVAIP | 20M | BF-A | 3x70AX(5AZN) | SUBSTITUIDO | BAHIANOS | MT | 37.76M | TX10 | 112,5KVA | 37.76M | V3-4 | BT | MT | 46M | DOS | BF-A | 1x3x120(70)AX | 36.87M | 3x70AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>3 | BF-A | 2 | 112,5KVA | 2x1/0AN(4ANA) | INSTALAÇÃO | 1x3x120(70)AX | BT | B1F</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1030,14 +1006,14 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35.33m</t>
+          <t>37.76m</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | V3-4 | BT | 3x70AX(5AZN) | MT | 35.33M | 35.33M | XX | P4-30 | 37.76M | 37.76M | C12X600112,5KVACE2112,5KVAIP | MT | BT | SMFL112,5KVAL1(2) | V4-5 | 3x70AX(5AZN)</t>
+          <t>BT | MT | 1x3x120(70)AX | 3x70AX(5AZN) | 37.76M | 37.76M</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
@@ -1086,11 +1062,11 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>P2 | V1-2 | BT | TV. | 1x3x120(70)AX | MT | DOS | 3x70AX(5AZN) | C12X300112,5KVACEAFS | SMTG112,5KVA1AF(1) | BAHIANOS | 112,5KVA | TX10 | BF-A | 46M | 36.87M | 36.97M | 15KV_1F1(A) | E4-BF112,5KVAIP | (DCIM) | LC | (DCIM) | 30.55M | 112,5KVA | 112,5KVA | (DCIM) | NF | 30K</t>
+          <t>BT | TV. | 1x3x120(70)AX | MT | DOS | 3x70AX(5AZN) | C12X300112,5KVACEAFS | SMTG112,5KVA1AF(1)</t>
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1124,18 +1100,18 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36.87m</t>
+          <t>30.55m</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>TV. | 1x3x120(70)AX | V1-2 | BT | DOS | 3x70AX(5AZN) | MT | BAHIANOS | P2 | 36.87M | 36.97M | C12X300112,5KVACEAFS | MT | B1F | 112,5KVA | BT | SMTG112,5KVA1AF(1) | 112,5KVA | 46M | BF-A | 1x3x120(70)AX | BF-A | 3x70AX(5AZN) | 30K | TX10 | 112,5KVA | 30.55M</t>
+          <t>NF | BT | 1x3x120(70)AX | MT | 3x185AX(5AZN) | 15KV_1F1(A)</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1168,27 +1144,19 @@
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>CONCRETO</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>P1-11 | NF | 15KV_1F1(A) | 566997 | BF-A | V9-1 | 112,5KVA | 30K | (DCIM) | 30K | E4-BF112,5KVAIP | 3x336AN | CONEX. | 112,5KVA | (DCIM) | BT | (DCIM) | 112,5KVA | 112,5KVA | (DCIM) | 112,5KVA(KL) | (DCIM) | CAMPO | 1x3x120(70)AX | C09x300,SMPI,IP | MT | 566997 | 3x185AX(5AZN) | LC | RAMAIS | 30K | 30K | 112,5KVA | 112,5KVA | CAMPO | 112,5KVA | BT | AVENIDA | BF-A | ANCORAR | 37,5KVA | (DCIM) | 112,5KVA | (DCIM) | 112,5KVA | 3x336AN | 37,5KVA | 112,5KVA | 37,5KVA | 112,5KVA | BF-A | ANCORAR | 400816F | (DCIM) | 112,5KVA | (DCIM) | 112,5KVA | 3x336AN | 37,5KVA | BF-A | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
+          <t>NF | BT | 1x3x120(70)AX | MT | 3x185AX(5AZN)</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>CRITICO</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1225,11 +1193,11 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>BT | V9-1 | MT | 1x3x120(70)AX | 3x185AX(5AZN) | NF | (DCIM) | P1-11 | (DCIM) | 30K | ANCORAR | 112,5KVA | BF-A | (DCIM) | (DCIM) | 112,5KVA | 37,5KVA | 30.55M | ANCORAR | 112,5KVA | CAMPO | BF-A | 112,5KVA | 31.38M | 400816F | 112,5KVA | 3x336AN | 112,5KVA | BT | 37,5KVA | 112,5KVA | 112,5KVA | 3x336AN | AVENIDA | 37,5KVA | 37,5KVA | 112,5KVA | 112,5KVA | 15KV_1F1(A) | 37,5KVA | 112,5KVA | 566997 | BF-A | E4-BF112,5KVAIP | (DCIM) | 112,5KVA | 30K</t>
+          <t>BT | MT | 1x3x120(70)AX | 3x185AX(5AZN) | NF | (DCIM) | (DCIM) | 0</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>

--- a/output_excel/17176272.xlsx
+++ b/output_excel/17176272.xlsx
@@ -32,11 +32,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="009C6500"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C6500"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="5">
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -470,20 +470,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,35 +512,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rua / Avenida</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ancoragem</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Lado Forte</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Metragem</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Altura Poste</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Informações</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Confiança</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Corrigido IA</t>
         </is>
@@ -565,20 +583,31 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>CONDIÇÕES | ODD | (DCIM) | ANCORAR | BF-A | 4 | 6 | 2 | BF-A | 7 | 7 | 112,5KVA | 2 | 7 | 2 | 6 | CAMPO | 6 | 7 | 112,5KVA | 7 | 1 | BT | 1 | 7 | AVENIDA | 7 | 1 | 1 | CONEX. | IP | (DCIM) | 1112,5KVA | 2 | AVENIDA | (DCIM) | (DCIM) | (DCIM) | 1 | 112,5KVA | 9 | (KL) | (DCIM) | 0 | 112,5KVA | 1 | 3 | 0 | BF-A | (KL) | 1 | 3 | BF-A | 1AF(1) | 0 | CONEX. | 16M | 1 | 0 | 2 | BF-A | (DCIM) | 1 | CONEX.</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>112,5KVA 2 4 7 6 2 V1-3 7 2 V1-3 | BT 112,5KVA CAMPO 1 7 6 2 7 6 2 7 | C12X300112,5KVACE1112,5KVAIP SMTG112,5KVAL1(2) | 1 QX16 | V7-8 BT 1x3x120(70)AX</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -603,27 +632,30 @@
           <t>V7-8</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>33.99m</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>BT | MT | 1x3x120(70)AX | 3x70AX(5AZN) | CABOS | ANCORAR | 3x336AN | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+          <t>33.99m</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>3x70AX(5AZN) 33.99M 33.99M | MT | 36.88M 36.88M | 2 V1-3 16M xP8 | MT BT 1x3x120(70)AX 3x70AX(5AZN) | 1 1 TX10 QX16 2 V1-3 2 V1-3 10M 7M | 1 1 BT JUQ CONEX. CONEX. 1 1 0 0 2 V1-3 2 V1-3 1 3 (DCIM)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -649,30 +681,33 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>CABOS | ANCORAR | 3x336AN | 112,5KVA | YOSHIDA | 7M | 112,5KVA | 10M | LC | BF-A | B1F | BF-A | CABOS | ANCORAR | (DCIM) | QX16 | TX10 | AV. | BT | MT | 1 | 1 | RAMAL | C12X300112,5KVACE1112,5KVAIP | BT | SMTG112,5KVAL1(2) | 1x3x120(70)AX | 3x70AX(5AZN) | BF-A | 16M | QX16 | 1 | 0 | 1 | BF-A | CONEX. | 1 | 3 | Q/R | (DCIM) | 1 | 0 | BF-A | 1 | 1 | CONEX. | 9 | BT | (DCIM) | 1</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVACE1112,5KVAIP SMTG112,5KVAL1(2) | LC P5 P7x | 112,5KVA CACHIMBO 112,5KVA | AV. (DCIM) | RAMAL</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -697,27 +732,30 @@
           <t>V6-7</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>36.88m</t>
-        </is>
-      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | MT | BT | 36.88M | AV. | (DCIM) | 36.88M | ANCORAR | CABOS | B1F | 112,5KVA</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="n">
+          <t>36.88m</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MT BT 1x3x120(70)AX 3x70AX(5AZN) | 36.88M 36.88M | P6 xBM | 3x70AX(5AZN) 37.01M 37.01M | 3x70AX(5AZN) 33.99M 33.99M | 1 1 TX10 QX16 2 V1-3 2 V1-3 10M 7M | RAMAL | MT</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -743,30 +781,33 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>BM | 566992 | BT | AV. | (DCIM) | 175ET005296879 | ANCORAR | BT | 13200 | BT | MT | CABOS | 33M | 1x3x120(70)AX | BF-A | 45KVA | BF-A | B1F | RAMAL | MT | 1x3x120(70)AX | 112,5KVA | LC | C10x600,B1M,M3F | 3x70AX(5AZN) | 3x70AX(5AZN) | INSTALAÇÃO | 1 | QX16 | YOSHIDA | BF-A | 7M | VEGETAL | TX10</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVACE1112,5KVAIP SMTG112,5KVAL1(2) | P6 xBM | C12X600112,5KVACE4112,5KVAIP | SMTR C12X300112,5KVACE-SH112,5KVAET4A112,5KVAIP | BT | 175ET005296879 566992 | AV. (DCIM) | V5-6 BT 1x3x120(70)AX</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -791,27 +832,30 @@
           <t>V5-6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>37.01m</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>BT | MT | 1x3x120(70)AX | 3x70AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+          <t>37.01m</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3x70AX(5AZN) 37.01M 37.01M | MT | P6 xBM | 29.14M 29.14M | MT BT 1x3x120(70)AX 3x70AX(5AZN) | SMPI 2 TX10 2 V1-3 33M | MT BT 1x3x120(70)AX 3x70AX(5AZN) | 36.88M 36.88M</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -839,20 +883,31 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>BT | MT | 1x3x120(70)AX | 3x70AX(5AZN) | 33M</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVACE4112,5KVAIP | C12X600112,5KVACE2112,5KVAIP | V5-6 BT 1x3x120(70)AX | C12X300112,5KVACE1112,5KVAIP SMTG112,5KVAL1(2) | 2X[,SMFL112,5KVAL1(2) 3 RAMAIS | LC P5 27.63m P5 | P6 xBM | V4-5</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -880,20 +935,31 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>BT | MT | 1x3x120(70)AX | XX | 3x70AX(5AZN) | LC</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>C12X600112,5KVACE2112,5KVAIP | C12X600112,5KVACE4112,5KVAIP | 2X[,SMFL112,5KVAL1(2) 3 RAMAIS | C12X300112,5KVACEAFS112,5KVASMTG112,5KVAL1(2)112,5KVAIP SUBSTITUIDO 1x4ANA | V4-5 | MT BT 1x3x120(70)AX 3x70AX(5AZN) | P4-30 XX | LC P5 27.63m P5</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -918,27 +984,30 @@
           <t>V4-5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29.14m</t>
-        </is>
-      </c>
+      <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1x3x120(70)AX | BT | 3x70AX(5AZN) | MT | 29.14M</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
+          <t>29.14m</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>MT BT 1x3x120(70)AX 3x70AX(5AZN) | 29.14M 29.14M | 2X[,SMFL112,5KVAL1(2) 3 RAMAIS | SMPI 2 TX10 2 V1-3 33M | 3x70AX(5AZN) 35.33M 35.33M | 3x70AX(5AZN) 37.01M 37.01M | MT | P6 xBM</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -966,20 +1035,31 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3 | BF-A | 2 | 112,5KVA | 2x1/0AN(4ANA) | INSTALAÇÃO | 1x3x120(70)AX | BT | B1F</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>12m</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>C12X300112,5KVACEAFS112,5KVASMTG112,5KVAL1(2)112,5KVAIP SUBSTITUIDO 1x4ANA | SMTG112,5KVA1AF(1) C12X300112,5KVACEAFS | P31 | C12X600112,5KVACE2112,5KVAIP | BAHIANOS 112,5KVA 2 | B1F BT 2 V1-3 3 1x3x120(70)AX | INSTALAÇÃO | MT 3x70AX(5AZN)</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1004,27 +1084,30 @@
           <t>V3-4</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37.76m</t>
-        </is>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>BT | MT | 1x3x120(70)AX | 3x70AX(5AZN) | 37.76M | 37.76M</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n">
+          <t>37.76m</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>37.76M | 3x70AX(5AZN) 35.33M 35.33M | MT | 37.76M | MT 3x70AX(5AZN) | MT BT 1x3x120(70)AX 3x70AX(5AZN) | 2X[,SMFL112,5KVAL1(2) 3 RAMAIS | 2 TX10 2 V1-3 20M</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1050,30 +1133,33 @@
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>CONCRETO</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>12m</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>BT | TV. | 1x3x120(70)AX | MT | DOS | 3x70AX(5AZN) | C12X300112,5KVACEAFS | SMTG112,5KVA1AF(1)</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SMTG112,5KVA1AF(1) C12X300112,5KVACEAFS | (DCIM) C09x300,SMPI,IP 12 CAMPO CONEX. (DCIM) 6112,5KVA(KL) 0 1 0 (DCIM)112,5KVA2 (DCIM) (DCIM) E4-BF112,5KVAIP | C12X300112,5KVACEAFS112,5KVASMTG112,5KVAL1(2)112,5KVAIP SUBSTITUIDO 1x4ANA | P2 DOS | BT V1-2 1x3x120(70)AX | TV. | BAHIANOS 112,5KVA 2 | NF</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1098,27 +1184,30 @@
           <t>V1-2</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30.55m</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>NF | BT | 1x3x120(70)AX | MT | 3x185AX(5AZN) | 15KV_1F1(A)</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+          <t>30.55m</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3x185AX(5AZN) 30.55M 31.38M | MT | 3 RAMAIS LC P5 | 3x70AX(5AZN) 36.97M 36.87M | MT | 2 TX10 2 V1-3 46M | BT V9-1 1x3x120(70)AX | P1-11</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1146,20 +1235,31 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>NF | BT | 1x3x120(70)AX | MT | 3x185AX(5AZN)</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>CRITICO</t>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9m</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>(DCIM) C09x300,SMPI,IP 12 CAMPO CONEX. (DCIM) 6112,5KVA(KL) 0 1 0 (DCIM)112,5KVA2 (DCIM) (DCIM) E4-BF112,5KVAIP | SMTG112,5KVA1AF(1) C12X300112,5KVACEAFS | NF | BT V9-1 1x3x120(70)AX | P1-11 | BF-A 566997 15KV_1F1(A) | (DCIM) | BT V1-2 1x3x120(70)AX</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1184,27 +1284,30 @@
           <t>V9-1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>30.55m</t>
-        </is>
-      </c>
+      <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>BT | MT | 1x3x120(70)AX | 3x185AX(5AZN) | NF | (DCIM) | (DCIM) | 0</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+          <t>30.55m</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3x185AX(5AZN) 30.55M 31.38M | MT | 3 RAMAIS LC P5 | BT V9-1 1x3x120(70)AX | 3x70AX(5AZN) 36.97M 36.87M | MT | 2 TX10 2 V1-3 46M | P1-11</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
